--- a/new-stats/ujpest-fc.xlsx
+++ b/new-stats/ujpest-fc.xlsx
@@ -917,22 +917,62 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ujpest</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zalaegerszeg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>

--- a/new-stats/ujpest-fc.xlsx
+++ b/new-stats/ujpest-fc.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Honved</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ujpest</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/ujpest-fc.xlsx
+++ b/new-stats/ujpest-fc.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ujpest</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Puskas Academy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/ujpest-fc.xlsx
+++ b/new-stats/ujpest-fc.xlsx
@@ -1091,22 +1091,62 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gyor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ujpest</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
